--- a/Knockouts/Mens.xlsx
+++ b/Knockouts/Mens.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\USER-PC\Ravens\Senior Open 2026\Knockouts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Ravens Seniors\Knockouts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE67C449-04DB-489B-BF63-814BE1DECFE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{752AD80B-6A8B-4BEE-91E6-AAA0C50298EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{6F46E828-8FFD-4531-838C-1A16471CA10A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" activeTab="1" xr2:uid="{6F46E828-8FFD-4531-838C-1A16471CA10A}"/>
   </bookViews>
   <sheets>
     <sheet name="Knockout Matches" sheetId="1" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="58">
   <si>
     <t>Match</t>
   </si>
@@ -103,69 +103,9 @@
     <t>Bye</t>
   </si>
   <si>
-    <t>G1W</t>
-  </si>
-  <si>
-    <t>G2W</t>
-  </si>
-  <si>
     <t>bye</t>
   </si>
   <si>
-    <t>G3W</t>
-  </si>
-  <si>
-    <t>G4W</t>
-  </si>
-  <si>
-    <t>G8W</t>
-  </si>
-  <si>
-    <t>G6W</t>
-  </si>
-  <si>
-    <t>G5W</t>
-  </si>
-  <si>
-    <t>G7W</t>
-  </si>
-  <si>
-    <t>G9W</t>
-  </si>
-  <si>
-    <t>G10W</t>
-  </si>
-  <si>
-    <t>G1R</t>
-  </si>
-  <si>
-    <t>G2R</t>
-  </si>
-  <si>
-    <t>G3R</t>
-  </si>
-  <si>
-    <t>G4R</t>
-  </si>
-  <si>
-    <t>G5R</t>
-  </si>
-  <si>
-    <t>G6R</t>
-  </si>
-  <si>
-    <t>G9R</t>
-  </si>
-  <si>
-    <t>G8R</t>
-  </si>
-  <si>
-    <t>G10R</t>
-  </si>
-  <si>
-    <t>G7R</t>
-  </si>
-  <si>
     <t>Day</t>
   </si>
   <si>
@@ -203,6 +143,99 @@
   </si>
   <si>
     <t>RAVENS TTC SENIER TOURNAMENT 2026</t>
+  </si>
+  <si>
+    <t>Shane Overmayer</t>
+  </si>
+  <si>
+    <t>Bounce TTC</t>
+  </si>
+  <si>
+    <t>Saaliegh Jabaar</t>
+  </si>
+  <si>
+    <t>NEXUS</t>
+  </si>
+  <si>
+    <t>Craig Fortuin</t>
+  </si>
+  <si>
+    <t>Quentin Thomas</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>Bernard Stewe</t>
+  </si>
+  <si>
+    <t>Goodwood</t>
+  </si>
+  <si>
+    <t>Thabiet Adams</t>
+  </si>
+  <si>
+    <t>Bishop Lavis</t>
+  </si>
+  <si>
+    <t>Muaath Adams</t>
+  </si>
+  <si>
+    <t>Dirk Coetzee</t>
+  </si>
+  <si>
+    <t>Duinefontein TTC</t>
+  </si>
+  <si>
+    <t>Joshua Du Plooy</t>
+  </si>
+  <si>
+    <t>Ravens</t>
+  </si>
+  <si>
+    <t>Sedick Abrahams</t>
+  </si>
+  <si>
+    <t>STEPH'S</t>
+  </si>
+  <si>
+    <t>Ashley Wesson</t>
+  </si>
+  <si>
+    <t>Liv Ken</t>
+  </si>
+  <si>
+    <t>Chris Sloster</t>
+  </si>
+  <si>
+    <t>Jodie Galant</t>
+  </si>
+  <si>
+    <t>Community House</t>
+  </si>
+  <si>
+    <t>Zahier Isaacs</t>
+  </si>
+  <si>
+    <t>Gaston Koetaan</t>
+  </si>
+  <si>
+    <t>David Nwafor</t>
+  </si>
+  <si>
+    <t>Kirshwan Steyn</t>
+  </si>
+  <si>
+    <t>Amien Phillips</t>
+  </si>
+  <si>
+    <t>Keenan Jooste</t>
+  </si>
+  <si>
+    <t>DJ Swanevelder</t>
+  </si>
+  <si>
+    <t>Maties</t>
   </si>
 </sst>
 </file>
@@ -377,12 +410,6 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -393,6 +420,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -841,16 +874,16 @@
         <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="K1" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="L1" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="M1" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
@@ -865,10 +898,10 @@
       </c>
       <c r="D2" t="str" cm="1">
         <f t="array" ref="D2:F2">'Knockout Grid'!A5:C5</f>
-        <v>G1W</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
+        <v>Shane Overmayer</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Bounce TTC</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -896,26 +929,26 @@
       </c>
       <c r="D3" t="str" cm="1">
         <f t="array" ref="D3:F3">'Knockout Grid'!A9:C9</f>
-        <v>G2R</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
+        <v>Jodie Galant</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Community House</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G3" t="str" cm="1">
         <f t="array" ref="G3:I3">'Knockout Grid'!A10:C10</f>
-        <v>G5R</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
+        <v>Quentin Thomas</v>
+      </c>
+      <c r="H3" t="str">
+        <v>TOP</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="K3" s="9">
         <v>46171</v>
@@ -939,10 +972,10 @@
       </c>
       <c r="D4" t="str" cm="1">
         <f t="array" ref="D4:F4">'Knockout Grid'!A13:C13</f>
-        <v>G10W</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
+        <v>Muaath Adams</v>
+      </c>
+      <c r="E4" t="str">
+        <v>NEXUS</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -980,10 +1013,10 @@
       </c>
       <c r="G5" t="str" cm="1">
         <f t="array" ref="G5:I5">'Knockout Grid'!A18:C18</f>
-        <v>G8W</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
+        <v>Joshua Du Plooy</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Ravens</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1001,10 +1034,10 @@
       </c>
       <c r="D6" t="str" cm="1">
         <f t="array" ref="D6:F6">'Knockout Grid'!A21:C21</f>
-        <v>G6W</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
+        <v>Bernard Stewe</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Goodwood</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -1042,10 +1075,10 @@
       </c>
       <c r="G7" t="str" cm="1">
         <f t="array" ref="G7:I7">'Knockout Grid'!A26:C26</f>
-        <v>G9W</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
+        <v>Ashley Wesson</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Liv Ken</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1063,26 +1096,26 @@
       </c>
       <c r="D8" t="str" cm="1">
         <f t="array" ref="D8:F8">'Knockout Grid'!A29:C29</f>
-        <v>G4R</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
+        <v>Amien Phillips</v>
+      </c>
+      <c r="E8" t="str">
+        <v>NEXUS</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8" t="str" cm="1">
         <f t="array" ref="G8:I8">'Knockout Grid'!A30:C30</f>
-        <v>G7R</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
+        <v>David Nwafor</v>
+      </c>
+      <c r="H8" t="str">
+        <v>Goodwood</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="K8" s="9">
         <v>46171</v>
@@ -1116,10 +1149,10 @@
       </c>
       <c r="G9" t="str" cm="1">
         <f t="array" ref="G9:I9">'Knockout Grid'!A34:C34</f>
-        <v>G3W</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
+        <v>Keenan Jooste</v>
+      </c>
+      <c r="H9" t="str">
+        <v>TOP</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -1137,10 +1170,10 @@
       </c>
       <c r="D10" t="str" cm="1">
         <f t="array" ref="D10:F10">'Knockout Grid'!A37:C37</f>
-        <v>G4W</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
+        <v>Kirshwan Steyn</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Ravens</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1168,10 +1201,10 @@
       </c>
       <c r="D11" t="str" cm="1">
         <f t="array" ref="D11:F11">'Knockout Grid'!A41:C41</f>
-        <v>G1R</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
+        <v>Saaliegh Jabaar</v>
+      </c>
+      <c r="E11" t="str">
+        <v>NEXUS</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1199,26 +1232,26 @@
       </c>
       <c r="D12" t="str" cm="1">
         <f t="array" ref="D12:F12">'Knockout Grid'!A45:C45</f>
-        <v>G8R</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
+        <v>Sedick Abrahams</v>
+      </c>
+      <c r="E12" t="str">
+        <v>STEPH'S</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G12" t="str" cm="1">
         <f t="array" ref="G12:I12">'Knockout Grid'!A46:C46</f>
-        <v>G10R</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
+        <v>Dirk Coetzee</v>
+      </c>
+      <c r="H12" t="str">
+        <v>Duinefontein TTC</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="K12" s="9">
         <v>46171</v>
@@ -1252,10 +1285,10 @@
       </c>
       <c r="G13" t="str" cm="1">
         <f t="array" ref="G13:I13">'Knockout Grid'!A50:C50</f>
-        <v>G5W</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
+        <v>Craig Fortuin</v>
+      </c>
+      <c r="H13" t="str">
+        <v>NEXUS</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -1273,10 +1306,10 @@
       </c>
       <c r="D14" t="str" cm="1">
         <f t="array" ref="D14:F14">'Knockout Grid'!A53:C53</f>
-        <v>G7W</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
+        <v>Gaston Koetaan</v>
+      </c>
+      <c r="E14" t="str">
+        <v>TOP</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1304,26 +1337,26 @@
       </c>
       <c r="D15" t="str" cm="1">
         <f t="array" ref="D15:F15">'Knockout Grid'!A57:C57</f>
-        <v>G3R</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
+        <v>DJ Swanevelder</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Maties</v>
       </c>
       <c r="F15">
         <v>0</v>
       </c>
       <c r="G15" t="str" cm="1">
         <f t="array" ref="G15:I15">'Knockout Grid'!A58:C58</f>
-        <v>G9R</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
+        <v>Chris Sloster</v>
+      </c>
+      <c r="H15" t="str">
+        <v>TOP</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="K15" s="9">
         <v>46171</v>
@@ -1347,10 +1380,10 @@
       </c>
       <c r="D16" t="str" cm="1">
         <f t="array" ref="D16:F16">'Knockout Grid'!A61:C61</f>
-        <v>G6R</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
+        <v>Thabiet Adams</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Bishop Lavis</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1388,10 +1421,10 @@
       </c>
       <c r="G17" t="str" cm="1">
         <f t="array" ref="G17:I17">'Knockout Grid'!A66:C66</f>
-        <v>G2W</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
+        <v>Zahier Isaacs</v>
+      </c>
+      <c r="H17" t="str">
+        <v>NEXUS</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1407,28 +1440,28 @@
       <c r="C18">
         <v>16</v>
       </c>
-      <c r="D18" cm="1">
+      <c r="D18" t="str" cm="1">
         <f t="array" ref="D18:F18">'Knockout Grid'!F7:H7</f>
-        <v>0</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
+        <v>Shane Overmayer</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Bounce TTC</v>
       </c>
       <c r="F18">
         <v>0</v>
       </c>
-      <c r="G18" cm="1">
+      <c r="G18" t="str" cm="1">
         <f t="array" ref="G18:I18">'Knockout Grid'!F8:H8</f>
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
+        <v>Jodie Galant</v>
+      </c>
+      <c r="H18" t="str">
+        <v>Community House</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
       <c r="J18" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="K18" s="9">
         <v>46172</v>
@@ -1450,28 +1483,28 @@
       <c r="C19">
         <v>16</v>
       </c>
-      <c r="D19" cm="1">
+      <c r="D19" t="str" cm="1">
         <f t="array" ref="D19:F19">'Knockout Grid'!F15:H15</f>
-        <v>0</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
+        <v>Muaath Adams</v>
+      </c>
+      <c r="E19" t="str">
+        <v>NEXUS</v>
       </c>
       <c r="F19">
         <v>0</v>
       </c>
-      <c r="G19" cm="1">
+      <c r="G19" t="str" cm="1">
         <f t="array" ref="G19:I19">'Knockout Grid'!F16:H16</f>
-        <v>0</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
+        <v>Joshua Du Plooy</v>
+      </c>
+      <c r="H19" t="str">
+        <v>Ravens</v>
       </c>
       <c r="I19">
         <v>0</v>
       </c>
       <c r="J19" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="K19" s="9">
         <v>46172</v>
@@ -1493,28 +1526,28 @@
       <c r="C20">
         <v>16</v>
       </c>
-      <c r="D20" cm="1">
+      <c r="D20" t="str" cm="1">
         <f t="array" ref="D20:F20">'Knockout Grid'!F23:H23</f>
-        <v>0</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
+        <v>Bernard Stewe</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Goodwood</v>
       </c>
       <c r="F20">
         <v>0</v>
       </c>
-      <c r="G20" cm="1">
+      <c r="G20" t="str" cm="1">
         <f t="array" ref="G20:I20">'Knockout Grid'!F24:H24</f>
-        <v>0</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
+        <v>Ashley Wesson</v>
+      </c>
+      <c r="H20" t="str">
+        <v>Liv Ken</v>
       </c>
       <c r="I20">
         <v>0</v>
       </c>
       <c r="J20" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="K20" s="9">
         <v>46172</v>
@@ -1536,28 +1569,28 @@
       <c r="C21">
         <v>16</v>
       </c>
-      <c r="D21" cm="1">
+      <c r="D21" t="str" cm="1">
         <f t="array" ref="D21:F21">'Knockout Grid'!F31:H31</f>
-        <v>0</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
+        <v>David Nwafor</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Goodwood</v>
       </c>
       <c r="F21">
         <v>0</v>
       </c>
-      <c r="G21" cm="1">
+      <c r="G21" t="str" cm="1">
         <f t="array" ref="G21:I21">'Knockout Grid'!F32:H32</f>
-        <v>0</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
+        <v>Keenan Jooste</v>
+      </c>
+      <c r="H21" t="str">
+        <v>TOP</v>
       </c>
       <c r="I21">
         <v>0</v>
       </c>
       <c r="J21" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="K21" s="9">
         <v>46172</v>
@@ -1579,28 +1612,28 @@
       <c r="C22">
         <v>16</v>
       </c>
-      <c r="D22" cm="1">
+      <c r="D22" t="str" cm="1">
         <f t="array" ref="D22:F22">'Knockout Grid'!F39:H39</f>
-        <v>0</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
+        <v>Kirshwan Steyn</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Ravens</v>
       </c>
       <c r="F22">
         <v>0</v>
       </c>
-      <c r="G22" cm="1">
+      <c r="G22" t="str" cm="1">
         <f t="array" ref="G22:I22">'Knockout Grid'!F40:H40</f>
-        <v>0</v>
-      </c>
-      <c r="H22">
-        <v>0</v>
+        <v>Saaliegh Jabaar</v>
+      </c>
+      <c r="H22" t="str">
+        <v>NEXUS</v>
       </c>
       <c r="I22">
         <v>0</v>
       </c>
       <c r="J22" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="K22" s="9">
         <v>46172</v>
@@ -1622,28 +1655,28 @@
       <c r="C23">
         <v>16</v>
       </c>
-      <c r="D23" cm="1">
+      <c r="D23" t="str" cm="1">
         <f t="array" ref="D23:F23">'Knockout Grid'!F47:H47</f>
-        <v>0</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
+        <v>Dirk Coetzee</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Duinefontein TTC</v>
       </c>
       <c r="F23">
         <v>0</v>
       </c>
-      <c r="G23" cm="1">
+      <c r="G23" t="str" cm="1">
         <f t="array" ref="G23:I23">'Knockout Grid'!F48:H48</f>
-        <v>0</v>
-      </c>
-      <c r="H23">
-        <v>0</v>
+        <v>Craig Fortuin</v>
+      </c>
+      <c r="H23" t="str">
+        <v>NEXUS</v>
       </c>
       <c r="I23">
         <v>0</v>
       </c>
       <c r="J23" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="K23" s="9">
         <v>46172</v>
@@ -1665,12 +1698,12 @@
       <c r="C24">
         <v>16</v>
       </c>
-      <c r="D24" cm="1">
+      <c r="D24" t="str" cm="1">
         <f t="array" ref="D24:F24">'Knockout Grid'!F55:H55</f>
-        <v>0</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
+        <v>Gaston Koetaan</v>
+      </c>
+      <c r="E24" t="str">
+        <v>TOP</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1686,7 +1719,7 @@
         <v>0</v>
       </c>
       <c r="J24" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="K24" s="9">
         <v>46172</v>
@@ -1708,28 +1741,28 @@
       <c r="C25">
         <v>16</v>
       </c>
-      <c r="D25" cm="1">
+      <c r="D25" t="str" cm="1">
         <f t="array" ref="D25:F25">'Knockout Grid'!F63:H63</f>
-        <v>0</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
+        <v>Thabiet Adams</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Bishop Lavis</v>
       </c>
       <c r="F25">
         <v>0</v>
       </c>
-      <c r="G25" cm="1">
+      <c r="G25" t="str" cm="1">
         <f t="array" ref="G25:I25">'Knockout Grid'!F64:H64</f>
-        <v>0</v>
-      </c>
-      <c r="H25">
-        <v>0</v>
+        <v>Zahier Isaacs</v>
+      </c>
+      <c r="H25" t="str">
+        <v>NEXUS</v>
       </c>
       <c r="I25">
         <v>0</v>
       </c>
       <c r="J25" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="K25" s="9">
         <v>46172</v>
@@ -1772,7 +1805,7 @@
         <v>0</v>
       </c>
       <c r="J26" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="K26" s="9">
         <v>46172</v>
@@ -1815,7 +1848,7 @@
         <v>0</v>
       </c>
       <c r="J27" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="K27" s="9">
         <v>46172</v>
@@ -1858,7 +1891,7 @@
         <v>0</v>
       </c>
       <c r="J28" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="K28" s="9">
         <v>46172</v>
@@ -1901,7 +1934,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="K29" s="9">
         <v>46172</v>
@@ -1944,7 +1977,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="K30" s="9">
         <v>46172</v>
@@ -1987,7 +2020,7 @@
         <v>0</v>
       </c>
       <c r="J31" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="K31" s="9">
         <v>46172</v>
@@ -2030,7 +2063,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="K32" s="9">
         <v>46172</v>
@@ -2069,93 +2102,93 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="34.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12"/>
-      <c r="N1" s="12"/>
-      <c r="O1" s="12"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="12"/>
-      <c r="R1" s="12"/>
-      <c r="S1" s="12"/>
-      <c r="T1" s="12"/>
-      <c r="U1" s="12"/>
-      <c r="V1" s="12"/>
-      <c r="W1" s="12"/>
+      <c r="A1" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
+      <c r="R1" s="17"/>
+      <c r="S1" s="17"/>
+      <c r="T1" s="17"/>
+      <c r="U1" s="17"/>
+      <c r="V1" s="17"/>
+      <c r="W1" s="17"/>
     </row>
     <row r="2" spans="1:23" ht="34.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="12"/>
-      <c r="N2" s="12"/>
-      <c r="O2" s="12"/>
-      <c r="P2" s="12"/>
-      <c r="Q2" s="12"/>
-      <c r="R2" s="12"/>
-      <c r="S2" s="12"/>
-      <c r="T2" s="12"/>
-      <c r="U2" s="12"/>
-      <c r="V2" s="12"/>
-      <c r="W2" s="12"/>
+      <c r="A2" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
+      <c r="R2" s="17"/>
+      <c r="S2" s="17"/>
+      <c r="T2" s="17"/>
+      <c r="U2" s="17"/>
+      <c r="V2" s="17"/>
+      <c r="W2" s="17"/>
     </row>
     <row r="3" spans="1:23" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A3" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
+      <c r="A3" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
       <c r="D3" s="11"/>
       <c r="E3" s="11"/>
-      <c r="F3" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
+      <c r="F3" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
       <c r="I3" s="11"/>
       <c r="J3" s="11"/>
-      <c r="K3" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
+      <c r="K3" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3" s="18"/>
+      <c r="M3" s="18"/>
       <c r="N3" s="11"/>
       <c r="O3" s="11"/>
-      <c r="P3" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q3" s="13"/>
-      <c r="R3" s="13"/>
+      <c r="P3" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q3" s="18"/>
+      <c r="R3" s="18"/>
       <c r="S3" s="11"/>
       <c r="T3" s="11"/>
-      <c r="U3" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="V3" s="13"/>
-      <c r="W3" s="13"/>
+      <c r="U3" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="V3" s="18"/>
+      <c r="W3" s="18"/>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
@@ -2169,14 +2202,16 @@
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="16"/>
+      <c r="A5" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="14"/>
       <c r="D5" s="2"/>
       <c r="F5" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="G5" s="9">
         <v>46172</v>
@@ -2189,11 +2224,11 @@
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="16"/>
+      <c r="A6" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="13"/>
+      <c r="C6" s="14"/>
       <c r="D6" s="3"/>
       <c r="F6">
         <v>17</v>
@@ -2207,7 +2242,7 @@
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="B7" s="9">
         <v>46171</v>
@@ -2219,9 +2254,13 @@
         <v>1</v>
       </c>
       <c r="E7" s="5"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="16"/>
+      <c r="F7" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="14"/>
       <c r="I7" s="2"/>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.25">
@@ -2235,21 +2274,29 @@
         <v>2</v>
       </c>
       <c r="D8" s="4"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="16"/>
+      <c r="F8" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" s="14"/>
       <c r="I8" s="1"/>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="16"/>
+      <c r="A9" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="14">
+        <v>3</v>
+      </c>
       <c r="D9" s="5"/>
       <c r="I9" s="4"/>
       <c r="K9" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="L9" s="9">
         <v>46172</v>
@@ -2262,11 +2309,15 @@
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="15"/>
-      <c r="C10" s="16"/>
+      <c r="A10" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="14">
+        <v>0</v>
+      </c>
       <c r="I10" s="4"/>
       <c r="K10">
         <v>25</v>
@@ -2281,9 +2332,9 @@
     <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="I11" s="4"/>
       <c r="J11" s="2"/>
-      <c r="K11" s="14"/>
-      <c r="L11" s="18"/>
-      <c r="M11" s="16"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="14"/>
       <c r="N11" s="2"/>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.25">
@@ -2297,20 +2348,22 @@
         <v>3</v>
       </c>
       <c r="I12" s="4"/>
-      <c r="K12" s="14"/>
-      <c r="L12" s="18"/>
-      <c r="M12" s="16"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="14"/>
       <c r="N12" s="1"/>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="16"/>
+      <c r="A13" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="14"/>
       <c r="D13" s="2"/>
       <c r="F13" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="G13" s="9">
         <v>46172</v>
@@ -2324,11 +2377,11 @@
       <c r="N13" s="4"/>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="15"/>
-      <c r="C14" s="16"/>
+      <c r="A14" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="13"/>
+      <c r="C14" s="14"/>
       <c r="D14" s="3"/>
       <c r="F14">
         <v>18</v>
@@ -2345,9 +2398,13 @@
     <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="D15" s="4"/>
       <c r="E15" s="5"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="16"/>
+      <c r="F15" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="H15" s="14"/>
       <c r="I15" s="5"/>
       <c r="N15" s="4"/>
     </row>
@@ -2362,21 +2419,25 @@
         <v>4</v>
       </c>
       <c r="D16" s="4"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="16"/>
+      <c r="F16" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="H16" s="14"/>
       <c r="N16" s="4"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" s="15"/>
-      <c r="C17" s="16"/>
+      <c r="A17" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="13"/>
+      <c r="C17" s="14"/>
       <c r="D17" s="5"/>
       <c r="N17" s="4"/>
       <c r="P17" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="Q17" s="9">
         <v>46172</v>
@@ -2389,11 +2450,13 @@
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" s="15"/>
-      <c r="C18" s="16"/>
+      <c r="A18" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="14"/>
       <c r="N18" s="4"/>
       <c r="P18">
         <v>29</v>
@@ -2408,9 +2471,9 @@
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="N19" s="4"/>
       <c r="O19" s="2"/>
-      <c r="P19" s="14"/>
-      <c r="Q19" s="18"/>
-      <c r="R19" s="16"/>
+      <c r="P19" s="12"/>
+      <c r="Q19" s="16"/>
+      <c r="R19" s="14"/>
       <c r="S19" s="2"/>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
@@ -2424,20 +2487,22 @@
         <v>5</v>
       </c>
       <c r="N20" s="4"/>
-      <c r="P20" s="14"/>
-      <c r="Q20" s="18"/>
-      <c r="R20" s="16"/>
+      <c r="P20" s="12"/>
+      <c r="Q20" s="16"/>
+      <c r="R20" s="14"/>
       <c r="S20" s="1"/>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21" s="15"/>
-      <c r="C21" s="16"/>
+      <c r="A21" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" s="14"/>
       <c r="D21" s="2"/>
       <c r="F21" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="G21" s="9">
         <v>46172</v>
@@ -2453,11 +2518,11 @@
       <c r="S21" s="4"/>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" s="15"/>
-      <c r="C22" s="16"/>
+      <c r="A22" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" s="13"/>
+      <c r="C22" s="14"/>
       <c r="D22" s="3"/>
       <c r="F22">
         <v>19</v>
@@ -2474,9 +2539,13 @@
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="D23" s="4"/>
       <c r="E23" s="5"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="16"/>
+      <c r="F23" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="H23" s="14"/>
       <c r="I23" s="2"/>
       <c r="N23" s="4"/>
       <c r="S23" s="4"/>
@@ -2492,23 +2561,27 @@
         <v>6</v>
       </c>
       <c r="D24" s="4"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="16"/>
+      <c r="F24" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="H24" s="14"/>
       <c r="I24" s="1"/>
       <c r="N24" s="4"/>
       <c r="S24" s="4"/>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A25" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" s="15"/>
-      <c r="C25" s="16"/>
+      <c r="A25" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" s="13"/>
+      <c r="C25" s="14"/>
       <c r="D25" s="5"/>
       <c r="I25" s="4"/>
       <c r="K25" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="L25" s="9">
         <v>46172</v>
@@ -2522,11 +2595,13 @@
       <c r="S25" s="4"/>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B26" s="15"/>
-      <c r="C26" s="16"/>
+      <c r="A26" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="C26" s="14"/>
       <c r="I26" s="4"/>
       <c r="K26">
         <v>26</v>
@@ -2542,7 +2617,7 @@
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="B27" s="9">
         <v>46171</v>
@@ -2555,9 +2630,9 @@
       </c>
       <c r="I27" s="4"/>
       <c r="J27" s="2"/>
-      <c r="K27" s="14"/>
-      <c r="L27" s="18"/>
-      <c r="M27" s="16"/>
+      <c r="K27" s="12"/>
+      <c r="L27" s="16"/>
+      <c r="M27" s="14"/>
       <c r="N27" s="5"/>
       <c r="S27" s="4"/>
     </row>
@@ -2572,20 +2647,24 @@
         <v>7</v>
       </c>
       <c r="I28" s="4"/>
-      <c r="K28" s="14"/>
-      <c r="L28" s="18"/>
-      <c r="M28" s="16"/>
+      <c r="K28" s="12"/>
+      <c r="L28" s="16"/>
+      <c r="M28" s="14"/>
       <c r="S28" s="4"/>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A29" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B29" s="15"/>
-      <c r="C29" s="16"/>
+      <c r="A29" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C29" s="14">
+        <v>0</v>
+      </c>
       <c r="D29" s="2"/>
       <c r="F29" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="G29" s="9">
         <v>46172</v>
@@ -2599,11 +2678,15 @@
       <c r="S29" s="4"/>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A30" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="B30" s="15"/>
-      <c r="C30" s="16"/>
+      <c r="A30" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" s="14">
+        <v>3</v>
+      </c>
       <c r="D30" s="3"/>
       <c r="F30">
         <v>20</v>
@@ -2620,9 +2703,13 @@
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="D31" s="4"/>
       <c r="E31" s="5"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="16"/>
+      <c r="F31" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="H31" s="14"/>
       <c r="I31" s="5"/>
       <c r="S31" s="4"/>
     </row>
@@ -2637,21 +2724,25 @@
         <v>8</v>
       </c>
       <c r="D32" s="4"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="15"/>
-      <c r="H32" s="16"/>
+      <c r="F32" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="G32" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="H32" s="14"/>
       <c r="S32" s="4"/>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A33" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" s="15"/>
-      <c r="C33" s="16"/>
+      <c r="A33" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B33" s="13"/>
+      <c r="C33" s="14"/>
       <c r="D33" s="5"/>
       <c r="S33" s="4"/>
       <c r="U33" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="V33" s="9">
         <v>46172</v>
@@ -2664,11 +2755,13 @@
       </c>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A34" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B34" s="15"/>
-      <c r="C34" s="16"/>
+      <c r="A34" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C34" s="14"/>
       <c r="S34" s="4"/>
       <c r="U34">
         <v>31</v>
@@ -2683,9 +2776,9 @@
     <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="S35" s="4"/>
       <c r="T35" s="2"/>
-      <c r="U35" s="14"/>
-      <c r="V35" s="18"/>
-      <c r="W35" s="16"/>
+      <c r="U35" s="12"/>
+      <c r="V35" s="16"/>
+      <c r="W35" s="14"/>
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
@@ -2698,19 +2791,21 @@
         <v>9</v>
       </c>
       <c r="S36" s="4"/>
-      <c r="U36" s="14"/>
-      <c r="V36" s="18"/>
-      <c r="W36" s="16"/>
+      <c r="U36" s="12"/>
+      <c r="V36" s="16"/>
+      <c r="W36" s="14"/>
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A37" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="B37" s="15"/>
-      <c r="C37" s="16"/>
+      <c r="A37" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C37" s="14"/>
       <c r="D37" s="2"/>
       <c r="F37" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="G37" s="9">
         <v>46172</v>
@@ -2725,11 +2820,11 @@
       <c r="V37" s="7"/>
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A38" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B38" s="15"/>
-      <c r="C38" s="16"/>
+      <c r="A38" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B38" s="13"/>
+      <c r="C38" s="14"/>
       <c r="D38" s="3"/>
       <c r="F38">
         <v>21</v>
@@ -2745,9 +2840,13 @@
     <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="D39" s="4"/>
       <c r="E39" s="5"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="15"/>
-      <c r="H39" s="16"/>
+      <c r="F39" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="G39" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="H39" s="14"/>
       <c r="I39" s="2"/>
       <c r="S39" s="4"/>
     </row>
@@ -2762,22 +2861,28 @@
         <v>10</v>
       </c>
       <c r="D40" s="4"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="15"/>
-      <c r="H40" s="16"/>
+      <c r="F40" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="G40" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="H40" s="14"/>
       <c r="I40" s="1"/>
       <c r="S40" s="4"/>
     </row>
     <row r="41" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A41" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B41" s="15"/>
-      <c r="C41" s="16"/>
+      <c r="A41" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B41" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C41" s="14"/>
       <c r="D41" s="5"/>
       <c r="I41" s="4"/>
       <c r="K41" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="L41" s="9">
         <v>46172</v>
@@ -2791,11 +2896,11 @@
       <c r="S41" s="4"/>
     </row>
     <row r="42" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A42" s="14" t="s">
+      <c r="A42" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B42" s="15"/>
-      <c r="C42" s="16"/>
+      <c r="B42" s="13"/>
+      <c r="C42" s="14"/>
       <c r="I42" s="4"/>
       <c r="K42">
         <v>27</v>
@@ -2810,7 +2915,7 @@
     </row>
     <row r="43" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="B43" s="9">
         <v>46171</v>
@@ -2823,9 +2928,9 @@
       </c>
       <c r="I43" s="4"/>
       <c r="J43" s="2"/>
-      <c r="K43" s="14"/>
-      <c r="L43" s="18"/>
-      <c r="M43" s="16"/>
+      <c r="K43" s="12"/>
+      <c r="L43" s="16"/>
+      <c r="M43" s="14"/>
       <c r="N43" s="2"/>
       <c r="S43" s="4"/>
     </row>
@@ -2840,21 +2945,25 @@
         <v>11</v>
       </c>
       <c r="I44" s="4"/>
-      <c r="K44" s="14"/>
-      <c r="L44" s="18"/>
-      <c r="M44" s="16"/>
+      <c r="K44" s="12"/>
+      <c r="L44" s="16"/>
+      <c r="M44" s="14"/>
       <c r="N44" s="1"/>
       <c r="S44" s="4"/>
     </row>
     <row r="45" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A45" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="B45" s="15"/>
-      <c r="C45" s="16"/>
+      <c r="A45" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B45" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C45" s="14">
+        <v>2</v>
+      </c>
       <c r="D45" s="2"/>
       <c r="F45" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="G45" s="9">
         <v>46172</v>
@@ -2869,11 +2978,15 @@
       <c r="S45" s="4"/>
     </row>
     <row r="46" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A46" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="B46" s="15"/>
-      <c r="C46" s="16"/>
+      <c r="A46" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C46" s="14">
+        <v>3</v>
+      </c>
       <c r="D46" s="3"/>
       <c r="F46">
         <v>22</v>
@@ -2891,9 +3004,13 @@
     <row r="47" spans="1:24" x14ac:dyDescent="0.25">
       <c r="D47" s="4"/>
       <c r="E47" s="5"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="15"/>
-      <c r="H47" s="16"/>
+      <c r="F47" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="G47" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="H47" s="14"/>
       <c r="I47" s="5"/>
       <c r="N47" s="4"/>
       <c r="S47" s="4"/>
@@ -2909,22 +3026,26 @@
         <v>12</v>
       </c>
       <c r="D48" s="4"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="15"/>
-      <c r="H48" s="16"/>
+      <c r="F48" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="G48" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="H48" s="14"/>
       <c r="N48" s="4"/>
       <c r="S48" s="4"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" s="15"/>
-      <c r="C49" s="16"/>
+      <c r="A49" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B49" s="13"/>
+      <c r="C49" s="14"/>
       <c r="D49" s="5"/>
       <c r="N49" s="4"/>
       <c r="P49" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="Q49" s="9">
         <v>46172</v>
@@ -2937,11 +3058,13 @@
       </c>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A50" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B50" s="15"/>
-      <c r="C50" s="16"/>
+      <c r="A50" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C50" s="14"/>
       <c r="N50" s="4"/>
       <c r="P50">
         <v>30</v>
@@ -2957,9 +3080,9 @@
     <row r="51" spans="1:19" x14ac:dyDescent="0.25">
       <c r="N51" s="4"/>
       <c r="O51" s="2"/>
-      <c r="P51" s="14"/>
-      <c r="Q51" s="18"/>
-      <c r="R51" s="16"/>
+      <c r="P51" s="12"/>
+      <c r="Q51" s="16"/>
+      <c r="R51" s="14"/>
       <c r="S51" s="5"/>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.25">
@@ -2973,29 +3096,31 @@
         <v>13</v>
       </c>
       <c r="N52" s="4"/>
-      <c r="P52" s="14"/>
-      <c r="Q52" s="18"/>
-      <c r="R52" s="16"/>
+      <c r="P52" s="12"/>
+      <c r="Q52" s="16"/>
+      <c r="R52" s="14"/>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A53" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B53" s="15"/>
-      <c r="C53" s="16"/>
+      <c r="A53" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="B53" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C53" s="14"/>
       <c r="D53" s="2"/>
       <c r="N53" s="4"/>
       <c r="Q53" s="7"/>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A54" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B54" s="15"/>
-      <c r="C54" s="16"/>
+      <c r="A54" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B54" s="13"/>
+      <c r="C54" s="14"/>
       <c r="D54" s="3"/>
       <c r="F54" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="G54" s="9">
         <v>46172</v>
@@ -3010,7 +3135,7 @@
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="B55" s="9">
         <v>46171</v>
@@ -3022,9 +3147,13 @@
         <v>4</v>
       </c>
       <c r="E55" s="5"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="15"/>
-      <c r="H55" s="16"/>
+      <c r="F55" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="G55" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="H55" s="14"/>
       <c r="I55" s="2"/>
       <c r="N55" s="4"/>
     </row>
@@ -3039,22 +3168,24 @@
         <v>14</v>
       </c>
       <c r="D56" s="4"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="15"/>
-      <c r="H56" s="16"/>
+      <c r="F56" s="12"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="14"/>
       <c r="I56" s="1"/>
       <c r="N56" s="4"/>
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A57" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B57" s="15"/>
-      <c r="C57" s="16"/>
+      <c r="A57" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="B57" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C57" s="14"/>
       <c r="D57" s="5"/>
       <c r="I57" s="4"/>
       <c r="K57" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="L57" s="9">
         <v>46172</v>
@@ -3067,11 +3198,13 @@
       </c>
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A58" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="B58" s="15"/>
-      <c r="C58" s="16"/>
+      <c r="A58" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B58" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C58" s="14"/>
       <c r="I58" s="4"/>
       <c r="K58">
         <v>28</v>
@@ -3087,9 +3220,9 @@
     <row r="59" spans="1:19" x14ac:dyDescent="0.25">
       <c r="I59" s="4"/>
       <c r="J59" s="2"/>
-      <c r="K59" s="14"/>
-      <c r="L59" s="18"/>
-      <c r="M59" s="16"/>
+      <c r="K59" s="12"/>
+      <c r="L59" s="16"/>
+      <c r="M59" s="14"/>
       <c r="N59" s="5"/>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.25">
@@ -3103,19 +3236,21 @@
         <v>15</v>
       </c>
       <c r="I60" s="4"/>
-      <c r="K60" s="14"/>
-      <c r="L60" s="18"/>
-      <c r="M60" s="16"/>
+      <c r="K60" s="12"/>
+      <c r="L60" s="16"/>
+      <c r="M60" s="14"/>
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A61" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="B61" s="15"/>
-      <c r="C61" s="16"/>
+      <c r="A61" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B61" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C61" s="14"/>
       <c r="D61" s="2"/>
       <c r="F61" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="G61" s="9">
         <v>46172</v>
@@ -3128,11 +3263,11 @@
       </c>
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A62" s="14" t="s">
+      <c r="A62" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B62" s="15"/>
-      <c r="C62" s="16"/>
+      <c r="B62" s="13"/>
+      <c r="C62" s="14"/>
       <c r="D62" s="3"/>
       <c r="F62">
         <v>24</v>
@@ -3148,9 +3283,13 @@
     <row r="63" spans="1:19" x14ac:dyDescent="0.25">
       <c r="D63" s="4"/>
       <c r="E63" s="5"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="15"/>
-      <c r="H63" s="16"/>
+      <c r="F63" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="G63" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="H63" s="14"/>
       <c r="I63" s="5"/>
     </row>
     <row r="64" spans="1:19" x14ac:dyDescent="0.25">
@@ -3164,24 +3303,30 @@
         <v>16</v>
       </c>
       <c r="D64" s="4"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="15"/>
-      <c r="H64" s="16"/>
+      <c r="F64" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G64" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="H64" s="14"/>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="14" t="s">
+      <c r="A65" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B65" s="15"/>
-      <c r="C65" s="16"/>
+      <c r="B65" s="13"/>
+      <c r="C65" s="14"/>
       <c r="D65" s="5"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B66" s="15"/>
-      <c r="C66" s="16"/>
+      <c r="A66" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="B66" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C66" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/Knockouts/Mens.xlsx
+++ b/Knockouts/Mens.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Ravens Seniors\Knockouts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{752AD80B-6A8B-4BEE-91E6-AAA0C50298EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AECE41CD-DC45-4953-8A76-31B71B779D0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" activeTab="1" xr2:uid="{6F46E828-8FFD-4531-838C-1A16471CA10A}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="58">
   <si>
     <t>Match</t>
   </si>
@@ -1343,7 +1343,7 @@
         <v>Maties</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" t="str" cm="1">
         <f t="array" ref="G15:I15">'Knockout Grid'!A58:C58</f>
@@ -1353,7 +1353,7 @@
         <v>TOP</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J15" s="9" t="s">
         <v>18</v>
@@ -1708,12 +1708,12 @@
       <c r="F24">
         <v>0</v>
       </c>
-      <c r="G24" cm="1">
+      <c r="G24" t="str" cm="1">
         <f t="array" ref="G24:I24">'Knockout Grid'!F56:H56</f>
-        <v>0</v>
-      </c>
-      <c r="H24">
-        <v>0</v>
+        <v>Chris Sloster</v>
+      </c>
+      <c r="H24" t="str">
+        <v>TOP</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -3168,8 +3168,12 @@
         <v>14</v>
       </c>
       <c r="D56" s="4"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="13"/>
+      <c r="F56" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G56" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="H56" s="14"/>
       <c r="I56" s="1"/>
       <c r="N56" s="4"/>
@@ -3181,7 +3185,9 @@
       <c r="B57" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="C57" s="14"/>
+      <c r="C57" s="14">
+        <v>1</v>
+      </c>
       <c r="D57" s="5"/>
       <c r="I57" s="4"/>
       <c r="K57" t="s">
@@ -3204,7 +3210,9 @@
       <c r="B58" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C58" s="14"/>
+      <c r="C58" s="14">
+        <v>3</v>
+      </c>
       <c r="I58" s="4"/>
       <c r="K58">
         <v>28</v>

--- a/Knockouts/Mens.xlsx
+++ b/Knockouts/Mens.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Ravens Seniors\Knockouts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AECE41CD-DC45-4953-8A76-31B71B779D0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D18E0D2-4286-4568-9C90-BB57D38D1D9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" activeTab="1" xr2:uid="{6F46E828-8FFD-4531-838C-1A16471CA10A}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="59">
   <si>
     <t>Match</t>
   </si>
@@ -236,6 +236,9 @@
   </si>
   <si>
     <t>Maties</t>
+  </si>
+  <si>
+    <t>WO</t>
   </si>
 </sst>
 </file>
@@ -431,7 +434,12 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="17">
+    <dxf>
+      <font>
+        <color theme="0" tint="-0.34998626667073579"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color theme="0" tint="-0.34998626667073579"/>
@@ -1448,7 +1456,7 @@
         <v>Bounce TTC</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G18" t="str" cm="1">
         <f t="array" ref="G18:I18">'Knockout Grid'!F8:H8</f>
@@ -1501,7 +1509,7 @@
         <v>Ravens</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J19" t="s">
         <v>19</v>
@@ -1534,7 +1542,7 @@
         <v>Goodwood</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G20" t="str" cm="1">
         <f t="array" ref="G20:I20">'Knockout Grid'!F24:H24</f>
@@ -1544,7 +1552,7 @@
         <v>Liv Ken</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="s">
         <v>19</v>
@@ -1587,7 +1595,7 @@
         <v>TOP</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J21" t="s">
         <v>19</v>
@@ -1620,7 +1628,7 @@
         <v>Ravens</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G22" t="str" cm="1">
         <f t="array" ref="G22:I22">'Knockout Grid'!F40:H40</f>
@@ -1630,7 +1638,7 @@
         <v>NEXUS</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" t="s">
         <v>19</v>
@@ -1662,8 +1670,8 @@
       <c r="E23" t="str">
         <v>Duinefontein TTC</v>
       </c>
-      <c r="F23">
-        <v>0</v>
+      <c r="F23" t="str">
+        <v>WO</v>
       </c>
       <c r="G23" t="str" cm="1">
         <f t="array" ref="G23:I23">'Knockout Grid'!F48:H48</f>
@@ -1673,7 +1681,7 @@
         <v>NEXUS</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J23" t="s">
         <v>19</v>
@@ -1716,7 +1724,7 @@
         <v>TOP</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J24" t="s">
         <v>19</v>
@@ -1759,7 +1767,7 @@
         <v>NEXUS</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J25" t="s">
         <v>19</v>
@@ -1784,22 +1792,22 @@
       <c r="C26" t="s">
         <v>9</v>
       </c>
-      <c r="D26" cm="1">
+      <c r="D26" t="str" cm="1">
         <f t="array" ref="D26:F26">'Knockout Grid'!K11:M11</f>
-        <v>0</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
+        <v>Shane Overmayer</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Bounce TTC</v>
       </c>
       <c r="F26">
         <v>0</v>
       </c>
-      <c r="G26" cm="1">
+      <c r="G26" t="str" cm="1">
         <f t="array" ref="G26:I26">'Knockout Grid'!K12:M12</f>
-        <v>0</v>
-      </c>
-      <c r="H26">
-        <v>0</v>
+        <v>Muaath Adams</v>
+      </c>
+      <c r="H26" t="str">
+        <v>NEXUS</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -1827,22 +1835,22 @@
       <c r="C27" t="s">
         <v>9</v>
       </c>
-      <c r="D27" cm="1">
+      <c r="D27" t="str" cm="1">
         <f t="array" ref="D27:F27">'Knockout Grid'!K27:M27</f>
-        <v>0</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
+        <v>Bernard Stewe</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Goodwood</v>
       </c>
       <c r="F27">
         <v>0</v>
       </c>
-      <c r="G27" cm="1">
+      <c r="G27" t="str" cm="1">
         <f t="array" ref="G27:I27">'Knockout Grid'!K28:M28</f>
-        <v>0</v>
-      </c>
-      <c r="H27">
-        <v>0</v>
+        <v>Keenan Jooste</v>
+      </c>
+      <c r="H27" t="str">
+        <v>TOP</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -1870,22 +1878,22 @@
       <c r="C28" t="s">
         <v>9</v>
       </c>
-      <c r="D28" cm="1">
+      <c r="D28" t="str" cm="1">
         <f t="array" ref="D28:F28">'Knockout Grid'!K43:M43</f>
-        <v>0</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
+        <v>Kirshwan Steyn</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Ravens</v>
       </c>
       <c r="F28">
         <v>0</v>
       </c>
-      <c r="G28" cm="1">
+      <c r="G28" t="str" cm="1">
         <f t="array" ref="G28:I28">'Knockout Grid'!K44:M44</f>
-        <v>0</v>
-      </c>
-      <c r="H28">
-        <v>0</v>
+        <v>Craig Fortuin</v>
+      </c>
+      <c r="H28" t="str">
+        <v>NEXUS</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -1913,22 +1921,22 @@
       <c r="C29" t="s">
         <v>9</v>
       </c>
-      <c r="D29" cm="1">
+      <c r="D29" t="str" cm="1">
         <f t="array" ref="D29:F29">'Knockout Grid'!K59:M59</f>
-        <v>0</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
+        <v>Chris Sloster</v>
+      </c>
+      <c r="E29" t="str">
+        <v>TOP</v>
       </c>
       <c r="F29">
         <v>0</v>
       </c>
-      <c r="G29" cm="1">
+      <c r="G29" t="str" cm="1">
         <f t="array" ref="G29:I29">'Knockout Grid'!K60:M60</f>
-        <v>0</v>
-      </c>
-      <c r="H29">
-        <v>0</v>
+        <v>Zahier Isaacs</v>
+      </c>
+      <c r="H29" t="str">
+        <v>NEXUS</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -2260,7 +2268,9 @@
       <c r="G7" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H7" s="14"/>
+      <c r="H7" s="14">
+        <v>3</v>
+      </c>
       <c r="I7" s="2"/>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.25">
@@ -2280,7 +2290,9 @@
       <c r="G8" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14">
+        <v>0</v>
+      </c>
       <c r="I8" s="1"/>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.25">
@@ -2332,8 +2344,12 @@
     <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="I11" s="4"/>
       <c r="J11" s="2"/>
-      <c r="K11" s="12"/>
-      <c r="L11" s="16"/>
+      <c r="K11" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>28</v>
+      </c>
       <c r="M11" s="14"/>
       <c r="N11" s="2"/>
     </row>
@@ -2348,8 +2364,12 @@
         <v>3</v>
       </c>
       <c r="I12" s="4"/>
-      <c r="K12" s="12"/>
-      <c r="L12" s="16"/>
+      <c r="K12" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>30</v>
+      </c>
       <c r="M12" s="14"/>
       <c r="N12" s="1"/>
     </row>
@@ -2404,7 +2424,9 @@
       <c r="G15" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="H15" s="14"/>
+      <c r="H15" s="14">
+        <v>0</v>
+      </c>
       <c r="I15" s="5"/>
       <c r="N15" s="4"/>
     </row>
@@ -2425,7 +2447,9 @@
       <c r="G16" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="H16" s="14"/>
+      <c r="H16" s="14">
+        <v>3</v>
+      </c>
       <c r="N16" s="4"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
@@ -2545,7 +2569,9 @@
       <c r="G23" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="H23" s="14"/>
+      <c r="H23" s="14">
+        <v>3</v>
+      </c>
       <c r="I23" s="2"/>
       <c r="N23" s="4"/>
       <c r="S23" s="4"/>
@@ -2567,7 +2593,9 @@
       <c r="G24" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>1</v>
+      </c>
       <c r="I24" s="1"/>
       <c r="N24" s="4"/>
       <c r="S24" s="4"/>
@@ -2630,8 +2658,12 @@
       </c>
       <c r="I27" s="4"/>
       <c r="J27" s="2"/>
-      <c r="K27" s="12"/>
-      <c r="L27" s="16"/>
+      <c r="K27" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>35</v>
+      </c>
       <c r="M27" s="14"/>
       <c r="N27" s="5"/>
       <c r="S27" s="4"/>
@@ -2647,8 +2679,12 @@
         <v>7</v>
       </c>
       <c r="I28" s="4"/>
-      <c r="K28" s="12"/>
-      <c r="L28" s="16"/>
+      <c r="K28" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>33</v>
+      </c>
       <c r="M28" s="14"/>
       <c r="S28" s="4"/>
     </row>
@@ -2709,7 +2745,9 @@
       <c r="G31" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="H31" s="14"/>
+      <c r="H31" s="14">
+        <v>0</v>
+      </c>
       <c r="I31" s="5"/>
       <c r="S31" s="4"/>
     </row>
@@ -2730,7 +2768,9 @@
       <c r="G32" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="H32" s="14"/>
+      <c r="H32" s="14">
+        <v>3</v>
+      </c>
       <c r="S32" s="4"/>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.25">
@@ -2846,7 +2886,9 @@
       <c r="G39" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="H39" s="14"/>
+      <c r="H39" s="14">
+        <v>3</v>
+      </c>
       <c r="I39" s="2"/>
       <c r="S39" s="4"/>
     </row>
@@ -2867,7 +2909,9 @@
       <c r="G40" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="H40" s="14"/>
+      <c r="H40" s="14">
+        <v>1</v>
+      </c>
       <c r="I40" s="1"/>
       <c r="S40" s="4"/>
     </row>
@@ -2928,8 +2972,12 @@
       </c>
       <c r="I43" s="4"/>
       <c r="J43" s="2"/>
-      <c r="K43" s="12"/>
-      <c r="L43" s="16"/>
+      <c r="K43" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>42</v>
+      </c>
       <c r="M43" s="14"/>
       <c r="N43" s="2"/>
       <c r="S43" s="4"/>
@@ -2945,8 +2993,12 @@
         <v>11</v>
       </c>
       <c r="I44" s="4"/>
-      <c r="K44" s="12"/>
-      <c r="L44" s="16"/>
+      <c r="K44" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>30</v>
+      </c>
       <c r="M44" s="14"/>
       <c r="N44" s="1"/>
       <c r="S44" s="4"/>
@@ -3010,7 +3062,9 @@
       <c r="G47" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="H47" s="14"/>
+      <c r="H47" s="14" t="s">
+        <v>58</v>
+      </c>
       <c r="I47" s="5"/>
       <c r="N47" s="4"/>
       <c r="S47" s="4"/>
@@ -3032,7 +3086,9 @@
       <c r="G48" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="H48" s="14"/>
+      <c r="H48" s="14">
+        <v>3</v>
+      </c>
       <c r="N48" s="4"/>
       <c r="S48" s="4"/>
     </row>
@@ -3153,7 +3209,9 @@
       <c r="G55" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="H55" s="14"/>
+      <c r="H55" s="14">
+        <v>0</v>
+      </c>
       <c r="I55" s="2"/>
       <c r="N55" s="4"/>
     </row>
@@ -3174,7 +3232,9 @@
       <c r="G56" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="H56" s="14"/>
+      <c r="H56" s="14">
+        <v>3</v>
+      </c>
       <c r="I56" s="1"/>
       <c r="N56" s="4"/>
     </row>
@@ -3228,8 +3288,12 @@
     <row r="59" spans="1:19" x14ac:dyDescent="0.25">
       <c r="I59" s="4"/>
       <c r="J59" s="2"/>
-      <c r="K59" s="12"/>
-      <c r="L59" s="16"/>
+      <c r="K59" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="L59" s="16" t="s">
+        <v>33</v>
+      </c>
       <c r="M59" s="14"/>
       <c r="N59" s="5"/>
     </row>
@@ -3244,8 +3308,12 @@
         <v>15</v>
       </c>
       <c r="I60" s="4"/>
-      <c r="K60" s="12"/>
-      <c r="L60" s="16"/>
+      <c r="K60" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="L60" s="16" t="s">
+        <v>30</v>
+      </c>
       <c r="M60" s="14"/>
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.25">
@@ -3297,7 +3365,9 @@
       <c r="G63" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="H63" s="14"/>
+      <c r="H63" s="14">
+        <v>0</v>
+      </c>
       <c r="I63" s="5"/>
     </row>
     <row r="64" spans="1:19" x14ac:dyDescent="0.25">
@@ -3317,7 +3387,9 @@
       <c r="G64" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="H64" s="14"/>
+      <c r="H64" s="14">
+        <v>3</v>
+      </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="12" t="s">
@@ -3348,82 +3420,82 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A5:A66">
-    <cfRule type="containsText" dxfId="15" priority="32" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="16" priority="32" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",A5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:F8">
-    <cfRule type="containsText" dxfId="14" priority="30" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="15" priority="30" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",F7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F16">
-    <cfRule type="containsText" dxfId="13" priority="28" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="14" priority="28" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",F15)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F23:F24">
-    <cfRule type="containsText" dxfId="12" priority="26" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="13" priority="26" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",F23)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31:F32">
-    <cfRule type="containsText" dxfId="11" priority="24" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="12" priority="24" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",F31)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F39:F40">
-    <cfRule type="containsText" dxfId="10" priority="22" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="11" priority="22" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",F39)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F47:F48">
-    <cfRule type="containsText" dxfId="9" priority="20" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="10" priority="20" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",F47)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F55:F56">
-    <cfRule type="containsText" dxfId="8" priority="18" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="9" priority="18" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",F55)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F63:F64">
-    <cfRule type="containsText" dxfId="7" priority="15" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="8" priority="15" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",F63)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11:K12">
-    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",K11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27:K28">
-    <cfRule type="containsText" dxfId="5" priority="9" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="6" priority="9" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",K27)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K43:K44">
-    <cfRule type="containsText" dxfId="4" priority="11" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="5" priority="11" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",K43)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K59:K60">
-    <cfRule type="containsText" dxfId="3" priority="13" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="4" priority="13" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",K59)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P19:P20">
-    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="3" priority="5" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",P19)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P51:P52">
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",P51)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U35:U36">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",U35)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Knockouts/Mens.xlsx
+++ b/Knockouts/Mens.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Ravens Seniors\Knockouts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D18E0D2-4286-4568-9C90-BB57D38D1D9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9509E1CB-6B80-43B5-9C83-9E05BF84070D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" activeTab="1" xr2:uid="{6F46E828-8FFD-4531-838C-1A16471CA10A}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="59">
   <si>
     <t>Match</t>
   </si>
@@ -434,12 +434,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.34998626667073579"/>
-      </font>
-    </dxf>
+  <dxfs count="16">
     <dxf>
       <font>
         <color theme="0" tint="-0.34998626667073579"/>
@@ -1800,7 +1795,7 @@
         <v>Bounce TTC</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G26" t="str" cm="1">
         <f t="array" ref="G26:I26">'Knockout Grid'!K12:M12</f>
@@ -1853,7 +1848,7 @@
         <v>TOP</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J27" t="s">
         <v>19</v>
@@ -1886,7 +1881,7 @@
         <v>Ravens</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G28" t="str" cm="1">
         <f t="array" ref="G28:I28">'Knockout Grid'!K44:M44</f>
@@ -1929,7 +1924,7 @@
         <v>TOP</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G29" t="str" cm="1">
         <f t="array" ref="G29:I29">'Knockout Grid'!K60:M60</f>
@@ -1939,7 +1934,7 @@
         <v>NEXUS</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J29" t="s">
         <v>19</v>
@@ -1964,22 +1959,22 @@
       <c r="C30" t="s">
         <v>10</v>
       </c>
-      <c r="D30" cm="1">
+      <c r="D30" t="str" cm="1">
         <f t="array" ref="D30:F30">'Knockout Grid'!P19:R19</f>
-        <v>0</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
+        <v>Shane Overmayer</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Bounce TTC</v>
       </c>
       <c r="F30">
         <v>0</v>
       </c>
-      <c r="G30" cm="1">
+      <c r="G30" t="str" cm="1">
         <f t="array" ref="G30:I30">'Knockout Grid'!P20:R20</f>
-        <v>0</v>
-      </c>
-      <c r="H30">
-        <v>0</v>
+        <v>Keenan Jooste</v>
+      </c>
+      <c r="H30" t="str">
+        <v>TOP</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -2007,22 +2002,22 @@
       <c r="C31" t="s">
         <v>10</v>
       </c>
-      <c r="D31" cm="1">
+      <c r="D31" t="str" cm="1">
         <f t="array" ref="D31:F31">'Knockout Grid'!P51:R51</f>
-        <v>0</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
+        <v>Kirshwan Steyn</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Ravens</v>
       </c>
       <c r="F31">
         <v>0</v>
       </c>
-      <c r="G31" cm="1">
+      <c r="G31" t="str" cm="1">
         <f t="array" ref="G31:I31">'Knockout Grid'!P52:R52</f>
-        <v>0</v>
-      </c>
-      <c r="H31">
-        <v>0</v>
+        <v>Chris Sloster</v>
+      </c>
+      <c r="H31" t="str">
+        <v>TOP</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -2350,7 +2345,9 @@
       <c r="L11" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="M11" s="14"/>
+      <c r="M11" s="14">
+        <v>3</v>
+      </c>
       <c r="N11" s="2"/>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.25">
@@ -2370,7 +2367,9 @@
       <c r="L12" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="M12" s="14"/>
+      <c r="M12" s="14">
+        <v>0</v>
+      </c>
       <c r="N12" s="1"/>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.25">
@@ -2495,8 +2494,12 @@
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="N19" s="4"/>
       <c r="O19" s="2"/>
-      <c r="P19" s="12"/>
-      <c r="Q19" s="16"/>
+      <c r="P19" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q19" s="16" t="s">
+        <v>28</v>
+      </c>
       <c r="R19" s="14"/>
       <c r="S19" s="2"/>
     </row>
@@ -2511,8 +2514,12 @@
         <v>5</v>
       </c>
       <c r="N20" s="4"/>
-      <c r="P20" s="12"/>
-      <c r="Q20" s="16"/>
+      <c r="P20" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q20" s="16" t="s">
+        <v>33</v>
+      </c>
       <c r="R20" s="14"/>
       <c r="S20" s="1"/>
     </row>
@@ -2664,7 +2671,9 @@
       <c r="L27" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="M27" s="14"/>
+      <c r="M27" s="14">
+        <v>0</v>
+      </c>
       <c r="N27" s="5"/>
       <c r="S27" s="4"/>
     </row>
@@ -2685,7 +2694,9 @@
       <c r="L28" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="M28" s="14"/>
+      <c r="M28" s="14">
+        <v>3</v>
+      </c>
       <c r="S28" s="4"/>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
@@ -2978,7 +2989,9 @@
       <c r="L43" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="M43" s="14"/>
+      <c r="M43" s="14">
+        <v>3</v>
+      </c>
       <c r="N43" s="2"/>
       <c r="S43" s="4"/>
     </row>
@@ -2999,7 +3012,9 @@
       <c r="L44" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="M44" s="14"/>
+      <c r="M44" s="14">
+        <v>0</v>
+      </c>
       <c r="N44" s="1"/>
       <c r="S44" s="4"/>
     </row>
@@ -3136,8 +3151,12 @@
     <row r="51" spans="1:19" x14ac:dyDescent="0.25">
       <c r="N51" s="4"/>
       <c r="O51" s="2"/>
-      <c r="P51" s="12"/>
-      <c r="Q51" s="16"/>
+      <c r="P51" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q51" s="16" t="s">
+        <v>42</v>
+      </c>
       <c r="R51" s="14"/>
       <c r="S51" s="5"/>
     </row>
@@ -3152,8 +3171,12 @@
         <v>13</v>
       </c>
       <c r="N52" s="4"/>
-      <c r="P52" s="12"/>
-      <c r="Q52" s="16"/>
+      <c r="P52" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q52" s="16" t="s">
+        <v>33</v>
+      </c>
       <c r="R52" s="14"/>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.25">
@@ -3294,7 +3317,9 @@
       <c r="L59" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="M59" s="14"/>
+      <c r="M59" s="14">
+        <v>3</v>
+      </c>
       <c r="N59" s="5"/>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.25">
@@ -3314,7 +3339,9 @@
       <c r="L60" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="M60" s="14"/>
+      <c r="M60" s="14">
+        <v>2</v>
+      </c>
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A61" s="12" t="s">
@@ -3420,82 +3447,82 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A5:A66">
-    <cfRule type="containsText" dxfId="16" priority="32" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="15" priority="32" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",A5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:F8">
-    <cfRule type="containsText" dxfId="15" priority="30" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="14" priority="30" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",F7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F16">
-    <cfRule type="containsText" dxfId="14" priority="28" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="13" priority="28" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",F15)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F23:F24">
-    <cfRule type="containsText" dxfId="13" priority="26" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="12" priority="26" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",F23)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31:F32">
-    <cfRule type="containsText" dxfId="12" priority="24" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="11" priority="24" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",F31)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F39:F40">
-    <cfRule type="containsText" dxfId="11" priority="22" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="10" priority="22" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",F39)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F47:F48">
-    <cfRule type="containsText" dxfId="10" priority="20" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="9" priority="20" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",F47)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F55:F56">
-    <cfRule type="containsText" dxfId="9" priority="18" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="8" priority="18" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",F55)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F63:F64">
-    <cfRule type="containsText" dxfId="8" priority="15" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="7" priority="15" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",F63)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11:K12">
-    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",K11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27:K28">
-    <cfRule type="containsText" dxfId="6" priority="9" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="5" priority="9" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",K27)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K43:K44">
-    <cfRule type="containsText" dxfId="5" priority="11" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="4" priority="11" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",K43)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K59:K60">
-    <cfRule type="containsText" dxfId="4" priority="13" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="3" priority="13" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",K59)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P19:P20">
-    <cfRule type="containsText" dxfId="3" priority="5" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",P19)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P51:P52">
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",P51)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U35:U36">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="Bye">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Bye">
       <formula>NOT(ISERROR(SEARCH("Bye",U35)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Knockouts/Mens.xlsx
+++ b/Knockouts/Mens.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Ravens Seniors\Knockouts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9509E1CB-6B80-43B5-9C83-9E05BF84070D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E995D74-00FD-4632-9865-6EE012A7473E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" activeTab="1" xr2:uid="{6F46E828-8FFD-4531-838C-1A16471CA10A}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="59">
   <si>
     <t>Match</t>
   </si>
@@ -1967,7 +1967,7 @@
         <v>Bounce TTC</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G30" t="str" cm="1">
         <f t="array" ref="G30:I30">'Knockout Grid'!P20:R20</f>
@@ -1977,7 +1977,7 @@
         <v>TOP</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J30" t="s">
         <v>19</v>
@@ -2010,7 +2010,7 @@
         <v>Ravens</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G31" t="str" cm="1">
         <f t="array" ref="G31:I31">'Knockout Grid'!P52:R52</f>
@@ -2045,22 +2045,22 @@
       <c r="C32" t="s">
         <v>11</v>
       </c>
-      <c r="D32" cm="1">
+      <c r="D32" t="str" cm="1">
         <f t="array" ref="D32:F32">'Knockout Grid'!U35:W35</f>
-        <v>0</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
+        <v>Shane Overmayer</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Bounce TTC</v>
       </c>
       <c r="F32">
         <v>0</v>
       </c>
-      <c r="G32" cm="1">
+      <c r="G32" t="str" cm="1">
         <f t="array" ref="G32:I32">'Knockout Grid'!U36:W36</f>
-        <v>0</v>
-      </c>
-      <c r="H32">
-        <v>0</v>
+        <v>Kirshwan Steyn</v>
+      </c>
+      <c r="H32" t="str">
+        <v>Ravens</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -2500,7 +2500,9 @@
       <c r="Q19" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="R19" s="14"/>
+      <c r="R19" s="14">
+        <v>3</v>
+      </c>
       <c r="S19" s="2"/>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
@@ -2520,7 +2522,9 @@
       <c r="Q20" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="R20" s="14"/>
+      <c r="R20" s="14">
+        <v>2</v>
+      </c>
       <c r="S20" s="1"/>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
@@ -2827,8 +2831,12 @@
     <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="S35" s="4"/>
       <c r="T35" s="2"/>
-      <c r="U35" s="12"/>
-      <c r="V35" s="16"/>
+      <c r="U35" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="V35" s="16" t="s">
+        <v>28</v>
+      </c>
       <c r="W35" s="14"/>
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.25">
@@ -2842,8 +2850,12 @@
         <v>9</v>
       </c>
       <c r="S36" s="4"/>
-      <c r="U36" s="12"/>
-      <c r="V36" s="16"/>
+      <c r="U36" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="V36" s="16" t="s">
+        <v>42</v>
+      </c>
       <c r="W36" s="14"/>
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.25">
@@ -3157,7 +3169,9 @@
       <c r="Q51" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="R51" s="14"/>
+      <c r="R51" s="14">
+        <v>3</v>
+      </c>
       <c r="S51" s="5"/>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.25">
@@ -3177,7 +3191,9 @@
       <c r="Q52" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="R52" s="14"/>
+      <c r="R52" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A53" s="12" t="s">

--- a/Knockouts/Mens.xlsx
+++ b/Knockouts/Mens.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Ravens Seniors\Knockouts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E995D74-00FD-4632-9865-6EE012A7473E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57FA373F-323D-4702-BF73-EFC77115168D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" activeTab="1" xr2:uid="{6F46E828-8FFD-4531-838C-1A16471CA10A}"/>
   </bookViews>
@@ -2053,7 +2053,7 @@
         <v>Bounce TTC</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G32" t="str" cm="1">
         <f t="array" ref="G32:I32">'Knockout Grid'!U36:W36</f>
@@ -2837,7 +2837,9 @@
       <c r="V35" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="W35" s="14"/>
+      <c r="W35" s="14">
+        <v>3</v>
+      </c>
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
@@ -2856,7 +2858,9 @@
       <c r="V36" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="W36" s="14"/>
+      <c r="W36" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
